--- a/output/pdf_financials_xlsx/BRCB.P.xlsx
+++ b/output/pdf_financials_xlsx/BRCB.P.xlsx
@@ -2812,19 +2812,19 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.08376599999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.08376599999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.08376599999999999</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.08376599999999999</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.08376599999999999</v>
       </c>
     </row>
     <row r="93">
@@ -4308,7 +4308,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BRCB.P.xlsx
+++ b/output/pdf_financials_xlsx/BRCB.P.xlsx
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.00015</v>
+        <v>0.0124</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.000163</v>
+        <v>0.13502</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.000132</v>
+        <v>0.028086</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7.7e-05</v>
+        <v>0.03502</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>5.1e-05</v>
+        <v>0.035474</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>5e-05</v>
+        <v>0.029359</v>
       </c>
     </row>
     <row r="11">
@@ -674,22 +674,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.00015</v>
+        <v>-0.0124</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.000163</v>
+        <v>-0.13502</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.000132</v>
+        <v>-0.028086</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-7.7e-05</v>
+        <v>-0.03502</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-5.1e-05</v>
+        <v>-0.035474</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-5e-05</v>
+        <v>-0.029359</v>
       </c>
     </row>
     <row r="12">
@@ -702,19 +702,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00101</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.012158</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02915</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02417</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01865</v>
       </c>
     </row>
     <row r="13">
@@ -1109,19 +1109,19 @@
         <v>-0.0124</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.13402</v>
+        <v>-0.13301</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.015928</v>
+        <v>-0.00377</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.00587</v>
+        <v>0.02328</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.011304</v>
+        <v>0.012866</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.011304</v>
+        <v>0.007346</v>
       </c>
     </row>
     <row r="28">
@@ -1159,19 +1159,19 @@
         <v>-0.0124</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.13402</v>
+        <v>-0.13301</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.015928</v>
+        <v>-0.00377</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.00587</v>
+        <v>0.02328</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.011304</v>
+        <v>0.012866</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.011304</v>
+        <v>0.007346</v>
       </c>
     </row>
     <row r="30">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.51485</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.692612</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.51485</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.692612</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRCB.P.xlsx
+++ b/output/pdf_financials_xlsx/BRCB.P.xlsx
@@ -2148,22 +2148,22 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.01225</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0125</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="68">
